--- a/reports/Debug-snowbowl-20251216/For The Week Ending (Prior Year)_Revenue.xlsx
+++ b/reports/Debug-snowbowl-20251216/For The Week Ending (Prior Year)_Revenue.xlsx
@@ -37,10 +37,10 @@
     <t xml:space="preserve">D1500                    </t>
   </si>
   <si>
+    <t xml:space="preserve">T100                     </t>
+  </si>
+  <si>
     <t xml:space="preserve">T103                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">T100                     </t>
   </si>
   <si>
     <t>Ski School</t>
@@ -486,7 +486,7 @@
         <v>6</v>
       </c>
       <c r="D3" s="2">
-        <v>1663.3400</v>
+        <v>94339.6400</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -500,7 +500,7 @@
         <v>6</v>
       </c>
       <c r="D4" s="2">
-        <v>94339.6400</v>
+        <v>1663.3400</v>
       </c>
     </row>
     <row r="5" spans="1:4">
